--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,115 +508,60 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>homeGoals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -687,10 +632,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -708,46 +653,9 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3" t="n">
         <v>45973.58333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,60 +508,75 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Odd_H_HT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_HT</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_H</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_A</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -632,20 +647,20 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.35</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>1.57</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
@@ -655,7 +670,16 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3" t="n">
         <v>45973.58333333334</v>
       </c>
     </row>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,6 +681,107 @@
       </c>
       <c r="AC2" s="3" t="n">
         <v>45973.58333333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>45973.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -757,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -757,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -638,22 +638,22 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -662,16 +662,16 @@
         <v>1.55</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -641,10 +641,10 @@
         <v>2.64</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.86</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -665,13 +665,13 @@
         <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -739,22 +739,22 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U3" t="n">
         <v>2.15</v>
@@ -763,16 +763,16 @@
         <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -650,36 +680,54 @@
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.38</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1.25</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA2" t="n">
         <v>2.3</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AB2" t="n">
         <v>1.55</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AC2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.08</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AF2" t="n">
         <v>1.65</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AG2" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
         <v>1.72</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
       </c>
     </row>
@@ -751,36 +799,54 @@
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.35</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.15</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AB3" t="n">
         <v>1.62</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AC3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="n">
         <v>1.73</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AH3" t="n">
         <v>2.06</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -668,13 +668,13 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="P2" t="n">
         <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.86</v>
+        <v>4.65</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -695,13 +695,13 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AA2" t="n">
         <v>2.3</v>
@@ -713,7 +713,7 @@
         <v>4.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
         <v>2.08</v>
@@ -787,7 +787,7 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
@@ -799,7 +799,7 @@
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
         <v>3</v>
@@ -814,13 +814,13 @@
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
         <v>2.15</v>
@@ -835,10 +835,10 @@
         <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
         <v>1.31</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="O2" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="P2" t="n">
         <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -695,37 +695,37 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
         <v>4.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
         <v>2.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
         <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.08</v>
@@ -820,31 +820,31 @@
         <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>4.2</v>
@@ -680,7 +680,7 @@
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
         <v>3.38</v>
@@ -698,19 +698,19 @@
         <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.15</v>
@@ -722,7 +722,7 @@
         <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
         <v>1.68</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.2</v>
@@ -823,10 +823,10 @@
         <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
         <v>4</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -668,19 +668,19 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="P2" t="n">
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="T2" t="n">
         <v>3.38</v>
@@ -713,16 +713,16 @@
         <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
         <v>2.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
         <v>1.68</v>
@@ -793,19 +793,19 @@
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -814,13 +814,13 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
         <v>2.15</v>
@@ -829,22 +829,22 @@
         <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="O2" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.7</v>
+        <v>5.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
         <v>8.699999999999999</v>
@@ -695,37 +695,37 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -790,37 +790,37 @@
         <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.33</v>
       </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA3" t="n">
         <v>2.15</v>
@@ -832,19 +832,19 @@
         <v>3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
         <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.58</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.3</v>
+        <v>4.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="P2" t="n">
         <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
@@ -683,10 +683,10 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
         <v>8.699999999999999</v>
@@ -704,10 +704,10 @@
         <v>2.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
         <v>4.4</v>
@@ -716,16 +716,16 @@
         <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.58</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.21</v>
@@ -823,10 +823,10 @@
         <v>2.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
         <v>3.8</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -668,13 +668,13 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.2</v>
+        <v>5.39</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
@@ -683,10 +683,10 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
         <v>8.699999999999999</v>
@@ -695,7 +695,7 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.35</v>
@@ -710,22 +710,22 @@
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
         <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -787,34 +787,34 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
         <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.3</v>
@@ -829,19 +829,19 @@
         <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
         <v>2.18</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>2.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>3.18</v>
@@ -689,19 +689,19 @@
         <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA2" t="n">
         <v>2.3</v>
@@ -710,22 +710,22 @@
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
         <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -787,10 +787,10 @@
         <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
@@ -805,22 +805,22 @@
         <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.99</v>
+        <v>3.27</v>
       </c>
       <c r="AA3" t="n">
         <v>2.15</v>
@@ -829,16 +829,16 @@
         <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
         <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
         <v>1.14</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
         <v>5</v>
@@ -671,10 +671,10 @@
         <v>2.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.45</v>
+        <v>5.29</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
@@ -698,34 +698,34 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -781,37 +781,37 @@
         <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -820,31 +820,31 @@
         <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="N2" t="n">
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.29</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
@@ -781,70 +781,70 @@
         <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.25</v>
       </c>
       <c r="P3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45973.85416666666</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -668,40 +668,40 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
         <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AA2" t="n">
         <v>2.3</v>
@@ -710,7 +710,7 @@
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD2" t="n">
         <v>1.15</v>
@@ -722,10 +722,10 @@
         <v>1.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>

--- a/jogos_2025-11-12.xlsx
+++ b/jogos_2025-11-12.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31</v>
+        <v>2.99</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,34 +698,34 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="Z2" t="n">
         <v>2.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45973.58333333334</v>
